--- a/outputs/evaluation/architecture/validation/gemini-3-5/CF_M05/run_2/CF_M05_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/validation/gemini-3-5/CF_M05/run_2/CF_M05_arch_eval.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -456,7 +461,10 @@
       <c r="C2" t="n">
         <v>0.8537</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>0.6195000000000001</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -475,6 +483,9 @@
         <v>0.8824</v>
       </c>
       <c r="D3" t="n">
+        <v>0.6522</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.9431</v>
       </c>
     </row>
@@ -491,6 +502,9 @@
         <v>0.7143</v>
       </c>
       <c r="D4" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.8064</v>
       </c>
     </row>
@@ -1201,7 +1215,6 @@
       <c r="D2" t="n">
         <v>0.7649</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1222,7 +1235,6 @@
           <t>['AU_17', 'AU_18']</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>AU_58</t>
@@ -1233,7 +1245,6 @@
           <t>client, server</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1252,7 +1263,6 @@
           <t>CF_M05_AU06, CF_M05_AU32</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CF_M05_AU24</t>
@@ -1283,7 +1293,6 @@
       <c r="D3" t="n">
         <v>0.7752</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1304,7 +1313,6 @@
           <t>['AU_31', 'AU_32']</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>AU_62</t>
@@ -1315,7 +1323,6 @@
           <t>controllers, services</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1334,7 +1341,6 @@
           <t>CF_M05_AU17, CF_M05_AU21</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CF_M05_AU25</t>
@@ -1390,13 +1396,11 @@
           <t>['AU_20']</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>AU_30</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Contract Layer (DTO/Mappers)</t>
@@ -1421,13 +1425,11 @@
           <t>CF_M05_P04</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CF_M05_AU20</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1448,7 +1450,6 @@
       <c r="D5" t="n">
         <v>0.7848000000000001</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1469,7 +1470,6 @@
           <t>['AU_23', 'AU_24', 'AU_25']</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>AU_59</t>
@@ -1480,7 +1480,6 @@
           <t>view, viewmodel, model</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1501,7 +1500,6 @@
           <t xml:space="preserve">CF_M05_AU14, CF_M05_AU13, CF_M05_AU15 </t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CF_M05_AU27</t>
@@ -1552,14 +1550,11 @@
           <t>57</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>AU_10</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Portal Microservice</t>
@@ -1586,13 +1581,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CF_M05_AU02</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1633,14 +1626,11 @@
           <t>57</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>AU_09</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Leader Microservice</t>
@@ -1666,13 +1656,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CF_M05_AU01</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1693,7 +1681,6 @@
       <c r="D8" t="n">
         <v>0.8161</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1714,7 +1701,6 @@
           <t>['AU_09', 'AU_10', 'AU_11', 'AU_12', 'AU_13']</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>AU_55</t>
@@ -1725,7 +1711,6 @@
           <t>leader, portal, access control, communication log, scheduler</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1744,7 +1729,6 @@
           <t>CF_M05_AU01, CF_M05_AU02, CF_M05_AU03, CF_M05_AU04, CF_M05_AU05, CF_M05_AU11, CF_M05_AU12</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CF_M05_AU22</t>
@@ -1795,14 +1779,11 @@
           <t>61</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>AU_17</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Client (Frontend)</t>
@@ -1828,13 +1809,11 @@
           <t>CF_M05_P02</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CF_M05_AU06</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1875,14 +1854,11 @@
           <t>59</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>AU_13</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Scheduler Microservice</t>
@@ -1911,13 +1887,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CF_M05_AU05</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1958,14 +1932,11 @@
           <t>58</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>AU_12</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Communication Log Microservice</t>
@@ -1994,13 +1965,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CF_M05_AU04</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2041,14 +2010,11 @@
           <t>58</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>AU_11</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Access Control Microservice</t>
@@ -2073,13 +2039,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CF_M05_AU03</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2120,14 +2084,11 @@
           <t>61</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>AU_18</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Server (Backend)</t>
@@ -2152,13 +2113,11 @@
           <t>CF_M05_P02</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>CF_M05_AU32</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2179,7 +2138,6 @@
       <c r="D14" t="n">
         <v>0.891</v>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -2200,7 +2158,6 @@
           <t>['AU_38', 'AU_33']</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>AU_65</t>
@@ -2211,7 +2168,6 @@
           <t>spring data, models</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -2230,7 +2186,6 @@
           <t>CF_M05_AU21, CF_M05_AU16</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>CF_M05_AU26</t>
@@ -2286,13 +2241,11 @@
           <t>['AU_20']</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>AU_26</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Presentation Layer (Controllers)</t>
@@ -2318,13 +2271,11 @@
           <t>CF_M05_P04</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>CF_M05_AU17</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2370,13 +2321,11 @@
           <t>['AU_20']</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>AU_28</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Data access layer (Repositories)</t>
@@ -2400,13 +2349,11 @@
           <t>CF_M05_P04</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>CF_M05_AU21</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2452,13 +2399,11 @@
           <t>['AU_20']</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>AU_29</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>Domain Layer (Models)</t>
@@ -2483,13 +2428,11 @@
           <t>CF_M05_P04</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>CF_M05_AU19</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2535,13 +2478,11 @@
           <t>['AU_20']</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>AU_27</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Business Logic Layer (Services)</t>
@@ -2565,13 +2506,11 @@
           <t>CF_M05_P04</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>CF_M05_AU18</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2612,14 +2551,11 @@
           <t>81</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>AU_45</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>Kubernetes</t>
@@ -2646,13 +2582,11 @@
           <t>CF_M05_AU07</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>CF_M05_AU35</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2698,13 +2632,11 @@
           <t>['AU_20']</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>P_05</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>Layered Architecture</t>
@@ -2726,14 +2658,11 @@
       <c r="P20" t="n">
         <v>68.69</v>
       </c>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>CF_M05_P04</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2774,14 +2703,11 @@
           <t>84</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>AU_50</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>SonarQube</t>
@@ -2808,13 +2734,11 @@
           <t>CF_M05_AU32</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>CF_M05_AU08</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2855,14 +2779,11 @@
           <t>60</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>P_02</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>Cloud Architecture</t>
@@ -2882,14 +2803,11 @@
       <c r="P22" t="n">
         <v>60</v>
       </c>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>CF_M05_P05</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2930,14 +2848,11 @@
           <t>60</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>AU_15</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>GSB</t>
@@ -2962,13 +2877,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>CF_M05_AU12</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3014,13 +2927,11 @@
           <t>['AU_18', 'AU_58']</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>AU_21</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>HTTP</t>
@@ -3045,13 +2956,11 @@
           <t>CF_M05_AU34</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>CF_M05_AU31</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3097,13 +3006,11 @@
           <t>['AU_19']</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>AU_23</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>View</t>
@@ -3129,13 +3036,11 @@
           <t>CF_M05_P03</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>CF_M05_AU13</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3181,13 +3086,11 @@
           <t>['AU_66']</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>AU_46</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>Docker</t>
@@ -3211,13 +3114,11 @@
           <t>CF_M05_AU32</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
           <t>CF_M05_AU33</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3258,14 +3159,11 @@
           <t>60</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>AU_14</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>Ordering</t>
@@ -3292,13 +3190,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
           <t>CF_M05_AU11</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3344,13 +3240,11 @@
           <t>['AU_16']</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>AU_44</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>Amazon EKS</t>
@@ -3376,13 +3270,11 @@
           <t>CF_M05_P05</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
           <t>CF_M05_AU07</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3428,13 +3320,11 @@
           <t>['AU_18']</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>AU_20</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>Spring Boot</t>
@@ -3460,13 +3350,11 @@
           <t>CF_M05_AU32</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
           <t>CF_M05_AU29</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3512,13 +3400,11 @@
           <t>['AU_19']</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>P_04</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>MVVM</t>
@@ -3538,14 +3424,11 @@
       <c r="P30" t="n">
         <v>62</v>
       </c>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
           <t>CF_M05_P03</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3591,13 +3474,11 @@
           <t>['AU_17']</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>AU_19</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
           <t>Angular</t>
@@ -3621,13 +3502,11 @@
           <t>CF_M05_AU06</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
           <t>CF_M05_AU30</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3668,14 +3547,11 @@
           <t>55</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>P_01</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
           <t>Microservices</t>
@@ -3694,14 +3570,11 @@
       <c r="P32" t="n">
         <v>56</v>
       </c>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3747,13 +3620,11 @@
           <t>['AU_19']</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>AU_25</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
           <t>Model</t>
@@ -3779,13 +3650,11 @@
           <t>CF_M05_P03</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
           <t>CF_M05_AU15</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3826,14 +3695,11 @@
           <t>61</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>P_03</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
           <t>Client-Server</t>
@@ -3854,7 +3720,6 @@
       <c r="P34" t="n">
         <v>61</v>
       </c>
-      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
         <is>
           <t>Design Pattern</t>
@@ -3865,7 +3730,6 @@
           <t>CF_M05_P02</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3911,13 +3775,11 @@
           <t>['AU_19']</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
           <t>AU_24</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
           <t>ViewModel</t>
@@ -3943,13 +3805,11 @@
           <t>CF_M05_P03</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr">
         <is>
           <t>CF_M05_AU14</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3995,13 +3855,11 @@
           <t>['AU_67']</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
           <t>AU_52</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
           <t>Grafana</t>
@@ -4025,13 +3883,11 @@
           <t>CF_M05_AU32</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
         <is>
           <t>CF_M05_AU09</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4105,7 +3961,6 @@
           <t>Volkswagen Group Services</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Volkswagen Group Services forma part del Grup Volkswagen, un grup d’empreses multinacional alemany i un dels majors fabricants d'automòbils del món, i existeix per donar suport exclusivament a les diferents empreses del grup a escala mundial.</t>
@@ -4141,7 +3996,6 @@
           <t>Integration Bus</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>A aquesta solució se li posa el nom de NiX UK i es desenvolupa a Espanya com una capa de serveis basada en la tecnologia cloud que proveeix de solucions i aplicacions dirigides als importadors del grup segons les necessitats del negoci.</t>
@@ -4177,7 +4031,6 @@
           <t>Cloud technology</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>A aquesta solució se li posa el nom de NiX UK i es desenvolupa a Espanya com una capa de serveis basada en la tecnologia cloud que proveeix de solucions i aplicacions dirigides als importadors del grup segons les necessitats del negoci.</t>
@@ -4213,7 +4066,6 @@
           <t>SEAT</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Aquest projecte, tot i que té com a possible clients totes les marques que formen part del grup Volkswagen, es centrarà en dos clients: SEAT i VGED.</t>
@@ -4249,7 +4101,6 @@
           <t>VGED</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Aquest projecte, tot i que té com a possible clients totes les marques que formen part del grup Volkswagen, es centrarà en dos clients: SEAT i VGED.</t>
@@ -4285,7 +4136,6 @@
           <t>AUDI</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Aquest últim engloba les marques d’AUDI, SKODA i VOLKSWAGEN.</t>
@@ -4321,7 +4171,6 @@
           <t>SKODA</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Aquest últim engloba les marques d’AUDI, SKODA i VOLKSWAGEN.</t>
@@ -4357,7 +4206,6 @@
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Aquest últim engloba les marques d’AUDI, SKODA i VOLKSWAGEN.</t>
@@ -4393,7 +4241,6 @@
           <t>Amazon Web Services</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>El proveïdor per aquest projecte és Amazon Web Services el qual té un ampli catàleg de serveis i recursos cloud.</t>
@@ -4429,7 +4276,6 @@
           <t>JSON</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>El protocol d’intercanvi de missatges que es fa servir en aquest cas és HTTP i el format de dades emprat és JSON.</t>
@@ -4465,7 +4311,6 @@
           <t>Controllers</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Dins de cada microservei hi ha una classe Controller per a cada model.</t>
@@ -4501,7 +4346,6 @@
           <t>Services</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Els serveis ofereixen la interfície i la implementació de tota la lògica de negoci de l’aplicació.</t>
@@ -4537,7 +4381,6 @@
           <t>Models</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Els models representen l’estructura interna i persistent de les entitats del sistema reflectint idènticament la informació emmagatzemada.</t>
@@ -4573,7 +4416,6 @@
           <t>DTOs</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>Els Data Transfer Objects (DTOs) actuen com a contenidors d’informació que permeten estructurar les dades necessàries per a cada petició...</t>
@@ -4609,7 +4451,6 @@
           <t>Mappers</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>Els Mappers són els responsables de la conversió entre els DTOs i els models.</t>
@@ -4645,7 +4486,6 @@
           <t>Repositories</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>Finalment, els Repositories s’encarreguen d’efectuar consultes sobre la base de dades.</t>
@@ -4681,7 +4521,6 @@
           <t>TypeScript</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>Angular és un framework de desenvolupament web creat per Google, basat en el llenguatge de programació superconjunt de JavaScript anomenat TypeScript...</t>
@@ -4717,7 +4556,6 @@
           <t>Spring Data</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>Spring Data és un projecte de Spring que simplifica l’accés i gestió de dades en aplicacions Java...</t>
@@ -4753,7 +4591,6 @@
           <t>Java Persistence API</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>...mentre que JPA (Java Persistence API) és una especificació que defineix com mapar objectes Java a bases de dades relacionals.</t>
@@ -4789,7 +4626,6 @@
           <t>Java</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>Aquesta tecnologia ens ajuda en la comunicació entre la capa de dades i la base de dades de l’aplicació del projecte. Tant aquesta tecnologia com les següents estan pensades per a ser utilitzades en desenvolupament d’aplicacions Java, el llenguatge que usarem al llarg del projecte.</t>
@@ -4825,7 +4661,6 @@
           <t>Java OpenJDK 17</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>OpenJDK és una implementació lliure i oberta del Java Development Kit (JDK), la plataforma per desenvolupar i executar aplicacions Java.</t>
@@ -4861,7 +4696,6 @@
           <t>IntelliJ IDEA</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>IntelliJ IDEA és un entorn de desenvolupament integrat (IDE) creat per JetBrains, pensat principalment per al desenvolupament de programari en Java...</t>
@@ -4897,7 +4731,6 @@
           <t>Visual Studio Code</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>Visual Studio Code és un editor de codi font lleuger, multiplataforma i gratuït desenvolupat per Microsoft...</t>
@@ -4933,7 +4766,6 @@
           <t>Amazon ECR</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>Aquestes imatges es guarden a l’Amazon ECR (Elastic Container Registry).</t>
@@ -4969,7 +4801,6 @@
           <t>JUnit 5</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>Per a les proves unitàries s’ha fet ús de les llibreries JUnit 5 i Mockito.</t>
@@ -5005,7 +4836,6 @@
           <t>Mockito</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>Per a les proves unitàries s’ha fet ús de les llibreries JUnit 5 i Mockito.</t>
@@ -5041,7 +4871,6 @@
           <t>Postman</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>Per a aquesta tasca s’ha fet ús de l’aplicació Postman per a poder provar les crides modifcades donat que no hi ha pantalles del microservei Ordering a l’aplicació.</t>
@@ -5077,7 +4906,6 @@
           <t>Spring Boot Actuator</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>Spring Boot té suport nadiu per exposar mètriques i informació de l’estat de l’aplicació a través del mòdul Spring Boot Actuator que després poden ser visualitzades a Grafana.</t>
@@ -5108,7 +4936,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>integration bus, cloud technology</t>
@@ -5144,7 +4971,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>ordering, gsb</t>
@@ -5180,7 +5006,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
           <t>client, server</t>
@@ -5216,7 +5041,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
           <t>presentation layer, business logic layer, data access layer, domain layer, cross-cutting contract layer</t>
@@ -5252,7 +5076,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
           <t>controllers, services</t>
@@ -5288,7 +5111,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
           <t>dtos, mappers, models</t>
@@ -5324,7 +5146,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
           <t>repositories, models</t>
@@ -5360,7 +5181,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
           <t>docker, amazon ecr</t>
@@ -5396,7 +5216,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
           <t>spring boot actuator, grafana</t>
@@ -5493,7 +5312,6 @@
           <t>Amazon RDS</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t xml:space="preserve"> the microservices are connected to a shared database (Amazon RDS) that is decoupled per
@@ -5530,7 +5348,6 @@
           <t>Database</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>the microservices are connected to a shared database that is decoupled per
@@ -5563,7 +5380,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>communication log microservice, leader microservice, portal microservice, access control microservice, scheduler microservice, client (frontend), amazon eks</t>
@@ -5579,7 +5395,6 @@
           <t>AU_55</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>0.7831</v>
       </c>
@@ -5600,7 +5415,6 @@
           <t>REST</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t xml:space="preserve">Data access and logic management in this project is carried out through REST operations, which
@@ -5612,7 +5426,6 @@
           <t>AU_62</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>0.7151999999999999</v>
       </c>
@@ -5628,7 +5441,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>viewmodel, server (backend)</t>
@@ -5644,7 +5456,6 @@
           <t>AU_62</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>0.7583</v>
       </c>
@@ -5665,7 +5476,6 @@
           <t>Shared Database</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>the microservices are connected to a shared database that is decoupled per
